--- a/artfynd/A 14539-2024 artfynd.xlsx
+++ b/artfynd/A 14539-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70438637</v>
+        <v>136829173</v>
       </c>
       <c r="B2" t="n">
-        <v>58195</v>
+        <v>57934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102122</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flodsångare</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Locustella fluviatilis</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wolf, 1810)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -721,9 +721,10 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vägskälet, Torrsjö mader, Sm</t>
@@ -760,22 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>04:05</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,43 +802,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70438637</t>
+          <t>https://artportalen.se/Sighting/136829173</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>28117072</v>
+        <v>70438637</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>58195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102122</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flodsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Locustella fluviatilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wolf, 1810)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -876,22 +888,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-01-04</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-01-04</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>04:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,33 +929,33 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/28117072</t>
+          <t>https://artportalen.se/Sighting/70438637</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>41126869</v>
+        <v>28117072</v>
       </c>
       <c r="B4" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,7 +965,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-01-03</t>
+          <t>2008-01-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-01-03</t>
+          <t>2008-01-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,6 +1044,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/28117072</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>41126869</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vägskälet, Torrsjö mader, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485761</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6405024</v>
+      </c>
+      <c r="S5" t="n">
+        <v>34</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Flisby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-01-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-01-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Heinrich</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Heinrich</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/41126869</t>
         </is>
@@ -1042,6 +1170,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14539-2024 artfynd.xlsx
+++ b/artfynd/A 14539-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136829173</v>
       </c>
       <c r="B2" t="n">
-        <v>57934</v>
+        <v>57947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14539-2024 artfynd.xlsx
+++ b/artfynd/A 14539-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136829173</v>
       </c>
       <c r="B2" t="n">
-        <v>57947</v>
+        <v>57949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14539-2024 artfynd.xlsx
+++ b/artfynd/A 14539-2024 artfynd.xlsx
@@ -714,16 +714,8 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 14539-2024 artfynd.xlsx
+++ b/artfynd/A 14539-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136829173</v>
       </c>
       <c r="B2" t="n">
-        <v>57949</v>
+        <v>57959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14539-2024 artfynd.xlsx
+++ b/artfynd/A 14539-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136829173</v>
       </c>
       <c r="B2" t="n">
-        <v>57959</v>
+        <v>57960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14539-2024 artfynd.xlsx
+++ b/artfynd/A 14539-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136829173</v>
       </c>
       <c r="B2" t="n">
-        <v>57960</v>
+        <v>57961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
